--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Permessi per sosta e circolazione (1).xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Permessi per sosta e circolazione (1).xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="148">
   <si>
     <r>
       <t xml:space="preserve">
@@ -334,6 +334,17 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t>Modifiche al piano urbano del traffico</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>Il tuo appuntamento</t>
     </r>
   </si>
   <si>
@@ -833,8 +844,8 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
-Se hai già provveduto a pagare l'avviso ignora questo messaggio.
+Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+Se hai già provveduto a pagare l'avviso, ignora questo messaggio.
 Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
 In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
     </r>
@@ -992,7 +1003,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> Puoi trovare in allegato a questo messaggio l'atto di rogito in formato </t>
+      <t xml:space="preserve"> Puoi trovare in allegato a questo messaggio il contrassegno in formato </t>
     </r>
     <r>
       <rPr>
@@ -1205,7 +1216,7 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">.
-Per rinnovarlo puoi seguire la [procedura di rinnovo online](URL) o prendere appuntamento presso </t>
+Per rinnovarlo puoi seguire la [procedura di rinnovo online](URL) o [prendere appuntamento presso lo sportello](URL) </t>
     </r>
     <r>
       <rPr>
@@ -1222,8 +1233,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">.
-Per prenotare il tuo appuntamento, [visita questo sito](URL).</t>
+      <t>.</t>
     </r>
   </si>
   <si>
@@ -1367,7 +1377,7 @@
     <t>Aggiungi documenti</t>
   </si>
   <si>
-    <t>Vedi Avviso</t>
+    <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
   </si>
   <si>
     <t>Prenota appuntamento</t>
@@ -2266,157 +2276,157 @@
         <v>82</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G4" s="33" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H4" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="J4" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="K4" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="L4" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="M4" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="N4" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="I4" s="33" t="s">
+      <c r="O4" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="J4" s="33" t="s">
-        <v>86</v>
-      </c>
-      <c r="K4" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="L4" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="M4" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="N4" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="O4" s="33" t="s">
-        <v>84</v>
-      </c>
       <c r="P4" s="33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q4" s="33" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="32" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H5" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="I5" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="J5" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="K5" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="L5" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="M5" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="N5" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="I5" s="34" t="s">
+      <c r="O5" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="J5" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="K5" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="L5" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="M5" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="N5" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="O5" s="34" t="s">
-        <v>98</v>
-      </c>
       <c r="P5" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q5" s="34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C6" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="E6" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="D6" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>107</v>
-      </c>
       <c r="F6" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G6" s="34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H6" s="34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I6" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J6" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K6" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="L6" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="M6" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="N6" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="L6" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="M6" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="N6" s="34" t="s">
-        <v>110</v>
-      </c>
       <c r="O6" s="34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P6" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q6" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>64</v>
@@ -2469,172 +2479,172 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I8" s="34" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J8" s="34" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K8" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L8" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M8" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N8" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O8" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P8" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q8" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F9" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="I9" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="G9" s="34" t="s">
-        <v>122</v>
-      </c>
-      <c r="H9" s="34" t="s">
-        <v>122</v>
-      </c>
-      <c r="I9" s="34" t="s">
-        <v>120</v>
-      </c>
       <c r="J9" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K9" s="34" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L9" s="34" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M9" s="34" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N9" s="34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O9" s="34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P9" s="34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q9" s="34" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F10" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="H10" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="I10" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="J10" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="K10" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="L10" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="M10" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="G10" s="34" t="s">
-        <v>135</v>
-      </c>
-      <c r="H10" s="34" t="s">
+      <c r="N10" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="I10" s="34" t="s">
+      <c r="O10" s="34" t="s">
         <v>137</v>
       </c>
-      <c r="J10" s="34" t="s">
-        <v>138</v>
-      </c>
-      <c r="K10" s="34" t="s">
-        <v>137</v>
-      </c>
-      <c r="L10" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="M10" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="N10" s="34" t="s">
-        <v>135</v>
-      </c>
-      <c r="O10" s="34" t="s">
-        <v>136</v>
-      </c>
       <c r="P10" s="34" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q10" s="34" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D11" s="34" t="s">
         <v>64</v>
@@ -2646,16 +2656,16 @@
         <v>64</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H11" s="34" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I11" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J11" s="34" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K11" s="34" t="s">
         <v>64</v>
@@ -2667,10 +2677,10 @@
         <v>64</v>
       </c>
       <c r="N11" s="34" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O11" s="34" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P11" s="34" t="s">
         <v>64</v>
